--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-10-2025.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.09</t>
+          <t>£10.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -813,7 +813,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£14.73</t>
+          <t>£14.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -935,7 +935,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£15.05</t>
+          <t>£15.00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£19.16</t>
+          <t>£19.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£20.89</t>
+          <t>£20.82</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£21.09</t>
+          <t>£21.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£24.21</t>
+          <t>£24.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£26.23</t>
+          <t>£26.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£25.94</t>
+          <t>£25.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£35.42</t>
+          <t>£35.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£31.68</t>
+          <t>£31.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£40.06</t>
+          <t>£40.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£39.05</t>
+          <t>£38.85</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£38.64</t>
+          <t>£38.48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£37.61</t>
+          <t>£37.42</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7a4dee955+80021]
-	GetHandleVerifier [0x0x7ff7a4dee9b0+80112]
-	(No symbol) [0x0x7ff7a4b7060f]
-	(No symbol) [0x0x7ff7a4bc8854]
-	(No symbol) [0x0x7ff7a4bc8b1c]
-	(No symbol) [0x0x7ff7a4c1c927]
-	(No symbol) [0x0x7ff7a4bf126f]
-	(No symbol) [0x0x7ff7a4c1968a]
-	(No symbol) [0x0x7ff7a4bf1003]
-	(No symbol) [0x0x7ff7a4bb95d1]
-	(No symbol) [0x0x7ff7a4bba3f3]
-	GetHandleVerifier [0x0x7ff7a50add0d+2960461]
-	GetHandleVerifier [0x0x7ff7a50a7fca+2936586]
-	GetHandleVerifier [0x0x7ff7a50c8a07+3070279]
-	GetHandleVerifier [0x0x7ff7a4e0843e+185214]
-	GetHandleVerifier [0x0x7ff7a4e0fe8f+216527]
-	GetHandleVerifier [0x0x7ff7a4df7b94+117460]
-	GetHandleVerifier [0x0x7ff7a4df7d4f+117903]
-	GetHandleVerifier [0x0x7ff7a4dddc28+11112]
+	GetHandleVerifier [0x0x7ff7259ee955+80021]
+	GetHandleVerifier [0x0x7ff7259ee9b0+80112]
+	(No symbol) [0x0x7ff72577060f]
+	(No symbol) [0x0x7ff7257c8854]
+	(No symbol) [0x0x7ff7257c8b1c]
+	(No symbol) [0x0x7ff72581c927]
+	(No symbol) [0x0x7ff7257f126f]
+	(No symbol) [0x0x7ff72581968a]
+	(No symbol) [0x0x7ff7257f1003]
+	(No symbol) [0x0x7ff7257b95d1]
+	(No symbol) [0x0x7ff7257ba3f3]
+	GetHandleVerifier [0x0x7ff725cadd0d+2960461]
+	GetHandleVerifier [0x0x7ff725ca7fca+2936586]
+	GetHandleVerifier [0x0x7ff725cc8a07+3070279]
+	GetHandleVerifier [0x0x7ff725a0843e+185214]
+	GetHandleVerifier [0x0x7ff725a0fe8f+216527]
+	GetHandleVerifier [0x0x7ff7259f7b94+117460]
+	GetHandleVerifier [0x0x7ff7259f7d4f+117903]
+	GetHandleVerifier [0x0x7ff7259ddc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
